--- a/complementarios_temperaturas/datos_mapa.xlsx
+++ b/complementarios_temperaturas/datos_mapa.xlsx
@@ -1221,7 +1221,7 @@
         <v>257</v>
       </c>
       <c r="L2">
-        <v>27.13666666666667</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1259,7 +1259,7 @@
         <v>257</v>
       </c>
       <c r="L3">
-        <v>27.94</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1294,7 +1294,7 @@
         <v>257</v>
       </c>
       <c r="L4">
-        <v>28.3</v>
+        <v>24.1304347826087</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1332,7 +1332,7 @@
         <v>257</v>
       </c>
       <c r="L5">
-        <v>26.27</v>
+        <v>22.71666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1370,7 +1370,7 @@
         <v>257</v>
       </c>
       <c r="L6">
-        <v>27.73333333333333</v>
+        <v>23.96333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1408,7 +1408,7 @@
         <v>257</v>
       </c>
       <c r="L7">
-        <v>28.56666666666667</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1446,7 +1446,7 @@
         <v>257</v>
       </c>
       <c r="L8">
-        <v>26.58666666666667</v>
+        <v>25.46333333333333</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1484,7 +1484,7 @@
         <v>257</v>
       </c>
       <c r="L9">
-        <v>27.48333333333333</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1522,7 +1522,7 @@
         <v>257</v>
       </c>
       <c r="L10">
-        <v>26.48888888888889</v>
+        <v>25.54444444444444</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1560,7 +1560,7 @@
         <v>257</v>
       </c>
       <c r="L11">
-        <v>27.93103448275862</v>
+        <v>26.77241379310345</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1598,7 +1598,7 @@
         <v>257</v>
       </c>
       <c r="L12">
-        <v>18.65666666666667</v>
+        <v>14.30666666666667</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1636,7 +1636,7 @@
         <v>257</v>
       </c>
       <c r="L13">
-        <v>24.85</v>
+        <v>22.51333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1674,7 +1674,7 @@
         <v>257</v>
       </c>
       <c r="L14">
-        <v>28.09</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1712,7 +1712,7 @@
         <v>257</v>
       </c>
       <c r="L15">
-        <v>27.24</v>
+        <v>26.15666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1747,7 +1747,7 @@
         <v>257</v>
       </c>
       <c r="L16">
-        <v>25.00588235294118</v>
+        <v>24.13529411764706</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1785,7 +1785,7 @@
         <v>257</v>
       </c>
       <c r="L17">
-        <v>26.47333333333334</v>
+        <v>25.63666666666667</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1823,7 +1823,7 @@
         <v>257</v>
       </c>
       <c r="L18">
-        <v>26.33</v>
+        <v>22.32068965517241</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1858,7 +1858,7 @@
         <v>257</v>
       </c>
       <c r="L19">
-        <v>26.35</v>
+        <v>22.37586206896552</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1893,7 +1893,7 @@
         <v>257</v>
       </c>
       <c r="L20">
-        <v>26.572</v>
+        <v>21.50384615384615</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1928,7 +1928,7 @@
         <v>257</v>
       </c>
       <c r="L21">
-        <v>21.39285714285714</v>
+        <v>17.12666666666667</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1963,7 +1963,7 @@
         <v>257</v>
       </c>
       <c r="L22">
-        <v>24.59666666666667</v>
+        <v>20.11333333333333</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1998,7 +1998,7 @@
         <v>257</v>
       </c>
       <c r="L23">
-        <v>26.1</v>
+        <v>22.03913043478261</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2033,7 +2033,7 @@
         <v>257</v>
       </c>
       <c r="L24">
-        <v>26.425</v>
+        <v>21.65454545454545</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2071,7 +2071,7 @@
         <v>257</v>
       </c>
       <c r="L25">
-        <v>24.01</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2144,7 +2144,7 @@
         <v>257</v>
       </c>
       <c r="L27">
-        <v>21.11333333333333</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2182,7 +2182,7 @@
         <v>257</v>
       </c>
       <c r="L28">
-        <v>24.57333333333333</v>
+        <v>21.39666666666666</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2220,7 +2220,7 @@
         <v>257</v>
       </c>
       <c r="L29">
-        <v>22.78666666666667</v>
+        <v>20.25333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2258,7 +2258,7 @@
         <v>257</v>
       </c>
       <c r="L30">
-        <v>21.69285714285714</v>
+        <v>19.91428571428571</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2296,7 +2296,7 @@
         <v>258</v>
       </c>
       <c r="L31">
-        <v>22.6</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2334,7 +2334,7 @@
         <v>257</v>
       </c>
       <c r="L32">
-        <v>21.56</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2372,7 +2372,7 @@
         <v>257</v>
       </c>
       <c r="L33">
-        <v>21.13703703703704</v>
+        <v>18.63333333333333</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2410,7 +2410,7 @@
         <v>257</v>
       </c>
       <c r="L34">
-        <v>22.06666666666667</v>
+        <v>18.71666666666667</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2483,7 +2483,7 @@
         <v>257</v>
       </c>
       <c r="L36">
-        <v>23.7</v>
+        <v>20.53333333333333</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2521,7 +2521,7 @@
         <v>257</v>
       </c>
       <c r="L37">
-        <v>21.95666666666667</v>
+        <v>19.11333333333333</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2559,7 +2559,7 @@
         <v>257</v>
       </c>
       <c r="L38">
-        <v>22.55333333333333</v>
+        <v>19.16896551724138</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2597,7 +2597,7 @@
         <v>257</v>
       </c>
       <c r="L39">
-        <v>22.78</v>
+        <v>18.13333333333333</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2632,7 +2632,7 @@
         <v>257</v>
       </c>
       <c r="L40">
-        <v>24.148</v>
+        <v>20.096</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2670,7 +2670,7 @@
         <v>257</v>
       </c>
       <c r="L41">
-        <v>23.656</v>
+        <v>19.61923076923077</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2708,7 +2708,7 @@
         <v>257</v>
       </c>
       <c r="L42">
-        <v>22.83703703703704</v>
+        <v>18.7962962962963</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2746,7 +2746,7 @@
         <v>257</v>
       </c>
       <c r="L43">
-        <v>22.96923076923077</v>
+        <v>18.29230769230769</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2784,7 +2784,7 @@
         <v>257</v>
       </c>
       <c r="L44">
-        <v>24.93333333333333</v>
+        <v>18.46666666666667</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2822,7 +2822,7 @@
         <v>257</v>
       </c>
       <c r="L45">
-        <v>27.54827586206897</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2860,7 +2860,7 @@
         <v>257</v>
       </c>
       <c r="L46">
-        <v>23.61</v>
+        <v>17.35666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2898,7 +2898,7 @@
         <v>257</v>
       </c>
       <c r="L47">
-        <v>23.29666666666667</v>
+        <v>17.15333333333333</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2936,7 +2936,7 @@
         <v>257</v>
       </c>
       <c r="L48">
-        <v>25.57333333333333</v>
+        <v>18.86666666666667</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2974,7 +2974,7 @@
         <v>257</v>
       </c>
       <c r="L49">
-        <v>23.375</v>
+        <v>16.93571428571429</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -3012,7 +3012,7 @@
         <v>257</v>
       </c>
       <c r="L50">
-        <v>17.04166666666667</v>
+        <v>10.63333333333333</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3050,7 +3050,7 @@
         <v>257</v>
       </c>
       <c r="L51">
-        <v>23.99090909090909</v>
+        <v>17.98260869565217</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -3088,7 +3088,7 @@
         <v>257</v>
       </c>
       <c r="L52">
-        <v>24.38888888888889</v>
+        <v>17.79259259259259</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3126,7 +3126,7 @@
         <v>257</v>
       </c>
       <c r="L53">
-        <v>25.54333333333333</v>
+        <v>19.00666666666667</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3164,7 +3164,7 @@
         <v>257</v>
       </c>
       <c r="L54">
-        <v>25.13666666666667</v>
+        <v>18.86</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3202,7 +3202,7 @@
         <v>257</v>
       </c>
       <c r="L55">
-        <v>24.22</v>
+        <v>17.95333333333333</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3240,7 +3240,7 @@
         <v>257</v>
       </c>
       <c r="L56">
-        <v>27.87666666666667</v>
+        <v>20.95666666666667</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3278,7 +3278,7 @@
         <v>257</v>
       </c>
       <c r="L57">
-        <v>27.75333333333333</v>
+        <v>20.95666666666667</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3316,7 +3316,7 @@
         <v>257</v>
       </c>
       <c r="L58">
-        <v>24.36785714285714</v>
+        <v>17.75862068965517</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3354,7 +3354,7 @@
         <v>257</v>
       </c>
       <c r="L59">
-        <v>26.41</v>
+        <v>19.39333333333333</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3392,7 +3392,7 @@
         <v>257</v>
       </c>
       <c r="L60">
-        <v>27.29666666666667</v>
+        <v>20.38333333333333</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3430,7 +3430,7 @@
         <v>257</v>
       </c>
       <c r="L61">
-        <v>27.49</v>
+        <v>20.64333333333333</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3468,7 +3468,7 @@
         <v>257</v>
       </c>
       <c r="L62">
-        <v>29.03793103448276</v>
+        <v>22.10689655172414</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3506,7 +3506,7 @@
         <v>257</v>
       </c>
       <c r="L63">
-        <v>28.79642857142857</v>
+        <v>22.02142857142857</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3544,7 +3544,7 @@
         <v>257</v>
       </c>
       <c r="L64">
-        <v>28.775</v>
+        <v>22.1625</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3582,7 +3582,7 @@
         <v>257</v>
       </c>
       <c r="L65">
-        <v>28.43</v>
+        <v>21.53333333333333</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3620,7 +3620,7 @@
         <v>257</v>
       </c>
       <c r="L66">
-        <v>30.39166666666667</v>
+        <v>23.875</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3658,7 +3658,7 @@
         <v>257</v>
       </c>
       <c r="L67">
-        <v>29.41851851851852</v>
+        <v>24.93333333333333</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3696,7 +3696,7 @@
         <v>257</v>
       </c>
       <c r="L68">
-        <v>25.98333333333333</v>
+        <v>22.58333333333333</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3734,7 +3734,7 @@
         <v>257</v>
       </c>
       <c r="L69">
-        <v>27.736</v>
+        <v>21.94583333333334</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3772,7 +3772,7 @@
         <v>257</v>
       </c>
       <c r="L70">
-        <v>28.69666666666667</v>
+        <v>22.54666666666667</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3810,7 +3810,7 @@
         <v>257</v>
       </c>
       <c r="L71">
-        <v>29.35333333333334</v>
+        <v>23.17666666666667</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3848,7 +3848,7 @@
         <v>257</v>
       </c>
       <c r="L72">
-        <v>31.70666666666667</v>
+        <v>25.98666666666667</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3886,7 +3886,7 @@
         <v>257</v>
       </c>
       <c r="L73">
-        <v>30.99</v>
+        <v>25.37666666666667</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3924,7 +3924,7 @@
         <v>257</v>
       </c>
       <c r="L74">
-        <v>27.71739130434782</v>
+        <v>24.18181818181818</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3962,7 +3962,7 @@
         <v>257</v>
       </c>
       <c r="L75">
-        <v>30.38</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4000,7 +4000,7 @@
         <v>257</v>
       </c>
       <c r="L76">
-        <v>26.26206896551724</v>
+        <v>23.35714285714286</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4038,7 +4038,7 @@
         <v>257</v>
       </c>
       <c r="L77">
-        <v>27.14333333333333</v>
+        <v>23.69666666666667</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4076,7 +4076,7 @@
         <v>257</v>
       </c>
       <c r="L78">
-        <v>28.21</v>
+        <v>24.07666666666666</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4114,7 +4114,7 @@
         <v>257</v>
       </c>
       <c r="L79">
-        <v>28.39333333333333</v>
+        <v>24.50666666666667</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4152,7 +4152,7 @@
         <v>257</v>
       </c>
       <c r="L80">
-        <v>30.41111111111111</v>
+        <v>25.57777777777778</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -4190,7 +4190,7 @@
         <v>257</v>
       </c>
       <c r="L81">
-        <v>30.44666666666667</v>
+        <v>25.56666666666667</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4228,7 +4228,7 @@
         <v>257</v>
       </c>
       <c r="L82">
-        <v>28.50344827586207</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4266,7 +4266,7 @@
         <v>257</v>
       </c>
       <c r="L83">
-        <v>28.53</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4304,7 +4304,7 @@
         <v>257</v>
       </c>
       <c r="L84">
-        <v>25.63666666666667</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4342,7 +4342,7 @@
         <v>257</v>
       </c>
       <c r="L85">
-        <v>27</v>
+        <v>20.56333333333333</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4380,7 +4380,7 @@
         <v>257</v>
       </c>
       <c r="L86">
-        <v>27.91071428571428</v>
+        <v>21.46071428571429</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4418,7 +4418,7 @@
         <v>257</v>
       </c>
       <c r="L87">
-        <v>25.252</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4456,7 +4456,7 @@
         <v>257</v>
       </c>
       <c r="L88">
-        <v>28</v>
+        <v>24.05333333333333</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4494,7 +4494,7 @@
         <v>257</v>
       </c>
       <c r="L89">
-        <v>27.57333333333333</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4532,7 +4532,7 @@
         <v>257</v>
       </c>
       <c r="L90">
-        <v>23.11333333333333</v>
+        <v>18.31333333333333</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4605,7 +4605,7 @@
         <v>257</v>
       </c>
       <c r="L92">
-        <v>25.78</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4643,7 +4643,7 @@
         <v>257</v>
       </c>
       <c r="L93">
-        <v>24.49666666666667</v>
+        <v>19.27666666666666</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4681,7 +4681,7 @@
         <v>257</v>
       </c>
       <c r="L94">
-        <v>23.90666666666667</v>
+        <v>18.37857142857143</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4719,7 +4719,7 @@
         <v>257</v>
       </c>
       <c r="L95">
-        <v>25.67666666666667</v>
+        <v>19.81666666666667</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4757,7 +4757,7 @@
         <v>257</v>
       </c>
       <c r="L96">
-        <v>27.12333333333333</v>
+        <v>21.36666666666667</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4795,7 +4795,7 @@
         <v>257</v>
       </c>
       <c r="L97">
-        <v>27.78214285714285</v>
+        <v>22.03214285714285</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4833,7 +4833,7 @@
         <v>257</v>
       </c>
       <c r="L98">
-        <v>25.92068965517242</v>
+        <v>19.84827586206897</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4871,7 +4871,7 @@
         <v>257</v>
       </c>
       <c r="L99">
-        <v>28.79666666666667</v>
+        <v>23.97</v>
       </c>
     </row>
   </sheetData>

--- a/complementarios_temperaturas/datos_mapa.xlsx
+++ b/complementarios_temperaturas/datos_mapa.xlsx
@@ -1221,7 +1221,7 @@
         <v>257</v>
       </c>
       <c r="L2">
-        <v>23.74</v>
+        <v>19.25666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1259,7 +1259,7 @@
         <v>257</v>
       </c>
       <c r="L3">
-        <v>23.89</v>
+        <v>19.00666666666667</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1294,7 +1294,7 @@
         <v>257</v>
       </c>
       <c r="L4">
-        <v>24.1304347826087</v>
+        <v>18.94166666666667</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1332,7 +1332,7 @@
         <v>257</v>
       </c>
       <c r="L5">
-        <v>22.71666666666667</v>
+        <v>18.05333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1370,7 +1370,7 @@
         <v>257</v>
       </c>
       <c r="L6">
-        <v>23.96333333333333</v>
+        <v>19.55333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1408,7 +1408,7 @@
         <v>257</v>
       </c>
       <c r="L7">
-        <v>26.68</v>
+        <v>24.17333333333334</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1446,7 +1446,7 @@
         <v>257</v>
       </c>
       <c r="L8">
-        <v>25.46333333333333</v>
+        <v>23.51034482758621</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1484,7 +1484,7 @@
         <v>257</v>
       </c>
       <c r="L9">
-        <v>26.09</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1522,7 +1522,7 @@
         <v>257</v>
       </c>
       <c r="L10">
-        <v>25.54444444444444</v>
+        <v>23.36666666666667</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1560,7 +1560,7 @@
         <v>257</v>
       </c>
       <c r="L11">
-        <v>26.77241379310345</v>
+        <v>24.77666666666666</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1598,7 +1598,7 @@
         <v>257</v>
       </c>
       <c r="L12">
-        <v>14.30666666666667</v>
+        <v>11.02962962962963</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1636,7 +1636,7 @@
         <v>257</v>
       </c>
       <c r="L13">
-        <v>22.51333333333333</v>
+        <v>19.61333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1674,7 +1674,7 @@
         <v>257</v>
       </c>
       <c r="L14">
-        <v>26.32</v>
+        <v>24.13333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1712,7 +1712,7 @@
         <v>257</v>
       </c>
       <c r="L15">
-        <v>26.15666666666667</v>
+        <v>24.23</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1747,7 +1747,7 @@
         <v>257</v>
       </c>
       <c r="L16">
-        <v>24.13529411764706</v>
+        <v>21.725</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1785,7 +1785,7 @@
         <v>257</v>
       </c>
       <c r="L17">
-        <v>25.63666666666667</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1823,7 +1823,7 @@
         <v>257</v>
       </c>
       <c r="L18">
-        <v>22.32068965517241</v>
+        <v>17.53666666666667</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1858,7 +1858,7 @@
         <v>257</v>
       </c>
       <c r="L19">
-        <v>22.37586206896552</v>
+        <v>17.27241379310345</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1893,7 +1893,7 @@
         <v>257</v>
       </c>
       <c r="L20">
-        <v>21.50384615384615</v>
+        <v>14.86538461538461</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1928,7 +1928,7 @@
         <v>257</v>
       </c>
       <c r="L21">
-        <v>17.12666666666667</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1963,7 +1963,7 @@
         <v>257</v>
       </c>
       <c r="L22">
-        <v>20.11333333333333</v>
+        <v>14.71333333333333</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1998,7 +1998,7 @@
         <v>257</v>
       </c>
       <c r="L23">
-        <v>22.03913043478261</v>
+        <v>17.04347826086957</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2033,7 +2033,7 @@
         <v>257</v>
       </c>
       <c r="L24">
-        <v>21.65454545454545</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2071,7 +2071,7 @@
         <v>257</v>
       </c>
       <c r="L25">
-        <v>21</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2144,7 +2144,7 @@
         <v>257</v>
       </c>
       <c r="L27">
-        <v>18.52</v>
+        <v>13.97333333333333</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2182,7 +2182,7 @@
         <v>257</v>
       </c>
       <c r="L28">
-        <v>21.39666666666666</v>
+        <v>16.58275862068966</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2220,7 +2220,7 @@
         <v>257</v>
       </c>
       <c r="L29">
-        <v>20.25333333333333</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2258,7 +2258,7 @@
         <v>257</v>
       </c>
       <c r="L30">
-        <v>19.91428571428571</v>
+        <v>15.47857142857143</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2296,7 +2296,7 @@
         <v>258</v>
       </c>
       <c r="L31">
-        <v>19.1</v>
+        <v>16.23846153846154</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2334,7 +2334,7 @@
         <v>257</v>
       </c>
       <c r="L32">
-        <v>19.63</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2372,7 +2372,7 @@
         <v>257</v>
       </c>
       <c r="L33">
-        <v>18.63333333333333</v>
+        <v>15.46666666666667</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2410,7 +2410,7 @@
         <v>257</v>
       </c>
       <c r="L34">
-        <v>18.71666666666667</v>
+        <v>14.58333333333333</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2483,7 +2483,7 @@
         <v>257</v>
       </c>
       <c r="L36">
-        <v>20.53333333333333</v>
+        <v>16.28333333333333</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2521,7 +2521,7 @@
         <v>257</v>
       </c>
       <c r="L37">
-        <v>19.11333333333333</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2559,7 +2559,7 @@
         <v>257</v>
       </c>
       <c r="L38">
-        <v>19.16896551724138</v>
+        <v>15.74333333333333</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2597,7 +2597,7 @@
         <v>257</v>
       </c>
       <c r="L39">
-        <v>18.13333333333333</v>
+        <v>14.06666666666667</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2632,7 +2632,7 @@
         <v>257</v>
       </c>
       <c r="L40">
-        <v>20.096</v>
+        <v>16.276</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2670,7 +2670,7 @@
         <v>257</v>
       </c>
       <c r="L41">
-        <v>19.61923076923077</v>
+        <v>15.42307692307692</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2708,7 +2708,7 @@
         <v>257</v>
       </c>
       <c r="L42">
-        <v>18.7962962962963</v>
+        <v>14.92592592592593</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2746,7 +2746,7 @@
         <v>257</v>
       </c>
       <c r="L43">
-        <v>18.29230769230769</v>
+        <v>13.284</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2784,7 +2784,7 @@
         <v>257</v>
       </c>
       <c r="L44">
-        <v>18.46666666666667</v>
+        <v>12.54666666666667</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2822,7 +2822,7 @@
         <v>257</v>
       </c>
       <c r="L45">
-        <v>21.62</v>
+        <v>15.85172413793103</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2860,7 +2860,7 @@
         <v>257</v>
       </c>
       <c r="L46">
-        <v>17.35666666666667</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2898,7 +2898,7 @@
         <v>257</v>
       </c>
       <c r="L47">
-        <v>17.15333333333333</v>
+        <v>10.94666666666667</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2936,7 +2936,7 @@
         <v>257</v>
       </c>
       <c r="L48">
-        <v>18.86666666666667</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2974,7 +2974,7 @@
         <v>257</v>
       </c>
       <c r="L49">
-        <v>16.93571428571429</v>
+        <v>11.17142857142857</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -3012,7 +3012,7 @@
         <v>257</v>
       </c>
       <c r="L50">
-        <v>10.63333333333333</v>
+        <v>5.445833333333333</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3050,7 +3050,7 @@
         <v>257</v>
       </c>
       <c r="L51">
-        <v>17.98260869565217</v>
+        <v>11.79130434782609</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -3088,7 +3088,7 @@
         <v>257</v>
       </c>
       <c r="L52">
-        <v>17.79259259259259</v>
+        <v>11.75555555555555</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3126,7 +3126,7 @@
         <v>257</v>
       </c>
       <c r="L53">
-        <v>19.00666666666667</v>
+        <v>12.69666666666667</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3164,7 +3164,7 @@
         <v>257</v>
       </c>
       <c r="L54">
-        <v>18.86</v>
+        <v>12.79333333333333</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3202,7 +3202,7 @@
         <v>257</v>
       </c>
       <c r="L55">
-        <v>17.95333333333333</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3240,7 +3240,7 @@
         <v>257</v>
       </c>
       <c r="L56">
-        <v>20.95666666666667</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3278,7 +3278,7 @@
         <v>257</v>
       </c>
       <c r="L57">
-        <v>20.95666666666667</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3316,7 +3316,7 @@
         <v>257</v>
       </c>
       <c r="L58">
-        <v>17.75862068965517</v>
+        <v>11.72758620689655</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3354,7 +3354,7 @@
         <v>257</v>
       </c>
       <c r="L59">
-        <v>19.39333333333333</v>
+        <v>13.52333333333333</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3392,7 +3392,7 @@
         <v>257</v>
       </c>
       <c r="L60">
-        <v>20.38333333333333</v>
+        <v>14.26666666666667</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3430,7 +3430,7 @@
         <v>257</v>
       </c>
       <c r="L61">
-        <v>20.64333333333333</v>
+        <v>14.46666666666667</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3468,7 +3468,7 @@
         <v>257</v>
       </c>
       <c r="L62">
-        <v>22.10689655172414</v>
+        <v>15.60344827586207</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3506,7 +3506,7 @@
         <v>257</v>
       </c>
       <c r="L63">
-        <v>22.02142857142857</v>
+        <v>15.94642857142857</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3544,7 +3544,7 @@
         <v>257</v>
       </c>
       <c r="L64">
-        <v>22.1625</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3582,7 +3582,7 @@
         <v>257</v>
       </c>
       <c r="L65">
-        <v>21.53333333333333</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3620,7 +3620,7 @@
         <v>257</v>
       </c>
       <c r="L66">
-        <v>23.875</v>
+        <v>18.10416666666667</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3658,7 +3658,7 @@
         <v>257</v>
       </c>
       <c r="L67">
-        <v>24.93333333333333</v>
+        <v>20.04444444444445</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3696,7 +3696,7 @@
         <v>257</v>
       </c>
       <c r="L68">
-        <v>22.58333333333333</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3734,7 +3734,7 @@
         <v>257</v>
       </c>
       <c r="L69">
-        <v>21.94583333333334</v>
+        <v>15.70416666666667</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3772,7 +3772,7 @@
         <v>257</v>
       </c>
       <c r="L70">
-        <v>22.54666666666667</v>
+        <v>16.50344827586207</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3810,7 +3810,7 @@
         <v>257</v>
       </c>
       <c r="L71">
-        <v>23.17666666666667</v>
+        <v>16.95333333333333</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3848,7 +3848,7 @@
         <v>257</v>
       </c>
       <c r="L72">
-        <v>25.98666666666667</v>
+        <v>20.17666666666667</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3886,7 +3886,7 @@
         <v>257</v>
       </c>
       <c r="L73">
-        <v>25.37666666666667</v>
+        <v>19.73333333333333</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3924,7 +3924,7 @@
         <v>257</v>
       </c>
       <c r="L74">
-        <v>24.18181818181818</v>
+        <v>19.72608695652174</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3962,7 +3962,7 @@
         <v>257</v>
       </c>
       <c r="L75">
-        <v>25.48</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4000,7 +4000,7 @@
         <v>257</v>
       </c>
       <c r="L76">
-        <v>23.35714285714286</v>
+        <v>19.57857142857143</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4038,7 +4038,7 @@
         <v>257</v>
       </c>
       <c r="L77">
-        <v>23.69666666666667</v>
+        <v>20.28666666666667</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4076,7 +4076,7 @@
         <v>257</v>
       </c>
       <c r="L78">
-        <v>24.07666666666666</v>
+        <v>20.12666666666667</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4114,7 +4114,7 @@
         <v>257</v>
       </c>
       <c r="L79">
-        <v>24.50666666666667</v>
+        <v>20.45333333333333</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4152,7 +4152,7 @@
         <v>257</v>
       </c>
       <c r="L80">
-        <v>25.57777777777778</v>
+        <v>20.34444444444444</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -4190,7 +4190,7 @@
         <v>257</v>
       </c>
       <c r="L81">
-        <v>25.56666666666667</v>
+        <v>20.17666666666667</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4228,7 +4228,7 @@
         <v>257</v>
       </c>
       <c r="L82">
-        <v>24.7</v>
+        <v>20.26666666666667</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4266,7 +4266,7 @@
         <v>257</v>
       </c>
       <c r="L83">
-        <v>24.9</v>
+        <v>20.47333333333334</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4304,7 +4304,7 @@
         <v>257</v>
       </c>
       <c r="L84">
-        <v>19.15</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4342,7 +4342,7 @@
         <v>257</v>
       </c>
       <c r="L85">
-        <v>20.56333333333333</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4380,7 +4380,7 @@
         <v>257</v>
       </c>
       <c r="L86">
-        <v>21.46071428571429</v>
+        <v>15.175</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4418,7 +4418,7 @@
         <v>257</v>
       </c>
       <c r="L87">
-        <v>19.32</v>
+        <v>13.424</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4456,7 +4456,7 @@
         <v>257</v>
       </c>
       <c r="L88">
-        <v>24.05333333333333</v>
+        <v>19.27333333333333</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4494,7 +4494,7 @@
         <v>257</v>
       </c>
       <c r="L89">
-        <v>23.52</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4532,7 +4532,7 @@
         <v>257</v>
       </c>
       <c r="L90">
-        <v>18.31333333333333</v>
+        <v>12.40666666666667</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4605,7 +4605,7 @@
         <v>257</v>
       </c>
       <c r="L92">
-        <v>20.12</v>
+        <v>13.81666666666667</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4643,7 +4643,7 @@
         <v>257</v>
       </c>
       <c r="L93">
-        <v>19.27666666666666</v>
+        <v>13.05333333333333</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4681,7 +4681,7 @@
         <v>257</v>
       </c>
       <c r="L94">
-        <v>18.37857142857143</v>
+        <v>12.54285714285714</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4719,7 +4719,7 @@
         <v>257</v>
       </c>
       <c r="L95">
-        <v>19.81666666666667</v>
+        <v>13.54333333333333</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4757,7 +4757,7 @@
         <v>257</v>
       </c>
       <c r="L96">
-        <v>21.36666666666667</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4795,7 +4795,7 @@
         <v>257</v>
       </c>
       <c r="L97">
-        <v>22.03214285714285</v>
+        <v>14.93571428571429</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4833,7 +4833,7 @@
         <v>257</v>
       </c>
       <c r="L98">
-        <v>19.84827586206897</v>
+        <v>13.36206896551724</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4871,7 +4871,7 @@
         <v>257</v>
       </c>
       <c r="L99">
-        <v>23.97</v>
+        <v>18.38333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/complementarios_temperaturas/datos_mapa.xlsx
+++ b/complementarios_temperaturas/datos_mapa.xlsx
@@ -1221,7 +1221,7 @@
         <v>257</v>
       </c>
       <c r="L2">
-        <v>19.25666666666667</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1259,7 +1259,7 @@
         <v>257</v>
       </c>
       <c r="L3">
-        <v>19.00666666666667</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1294,7 +1294,7 @@
         <v>257</v>
       </c>
       <c r="L4">
-        <v>18.94166666666667</v>
+        <v>15.94347826086956</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1332,7 +1332,7 @@
         <v>257</v>
       </c>
       <c r="L5">
-        <v>18.05333333333333</v>
+        <v>15.15666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1370,7 +1370,7 @@
         <v>257</v>
       </c>
       <c r="L6">
-        <v>19.55333333333333</v>
+        <v>16.71666666666667</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1408,7 +1408,7 @@
         <v>257</v>
       </c>
       <c r="L7">
-        <v>24.17333333333334</v>
+        <v>21.76333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1446,7 +1446,7 @@
         <v>257</v>
       </c>
       <c r="L8">
-        <v>23.51034482758621</v>
+        <v>21.82666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1484,7 +1484,7 @@
         <v>257</v>
       </c>
       <c r="L9">
-        <v>24.01</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1522,7 +1522,7 @@
         <v>257</v>
       </c>
       <c r="L10">
-        <v>23.36666666666667</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1560,7 +1560,7 @@
         <v>257</v>
       </c>
       <c r="L11">
-        <v>24.77666666666666</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1598,7 +1598,7 @@
         <v>257</v>
       </c>
       <c r="L12">
-        <v>11.02962962962963</v>
+        <v>8.825925925925926</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1636,7 +1636,7 @@
         <v>257</v>
       </c>
       <c r="L13">
-        <v>19.61333333333333</v>
+        <v>17.09333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1674,7 +1674,7 @@
         <v>257</v>
       </c>
       <c r="L14">
-        <v>24.13333333333333</v>
+        <v>22.09333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1712,7 +1712,7 @@
         <v>257</v>
       </c>
       <c r="L15">
-        <v>24.23</v>
+        <v>22.22666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1747,7 +1747,7 @@
         <v>257</v>
       </c>
       <c r="L16">
-        <v>21.725</v>
+        <v>20.18571428571429</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1785,7 +1785,7 @@
         <v>257</v>
       </c>
       <c r="L17">
-        <v>23.74</v>
+        <v>22.15666666666667</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1823,7 +1823,7 @@
         <v>257</v>
       </c>
       <c r="L18">
-        <v>17.53666666666667</v>
+        <v>14.59333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1858,7 +1858,7 @@
         <v>257</v>
       </c>
       <c r="L19">
-        <v>17.27241379310345</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1893,7 +1893,7 @@
         <v>257</v>
       </c>
       <c r="L20">
-        <v>14.86538461538461</v>
+        <v>10.96538461538462</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1928,7 +1928,7 @@
         <v>257</v>
       </c>
       <c r="L21">
-        <v>11.75</v>
+        <v>9.296666666666665</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1963,7 +1963,7 @@
         <v>257</v>
       </c>
       <c r="L22">
-        <v>14.71333333333333</v>
+        <v>11.76333333333333</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1998,7 +1998,7 @@
         <v>257</v>
       </c>
       <c r="L23">
-        <v>17.04347826086957</v>
+        <v>13.93636363636364</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2033,7 +2033,7 @@
         <v>257</v>
       </c>
       <c r="L24">
-        <v>16.5</v>
+        <v>12.62727272727273</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2071,7 +2071,7 @@
         <v>257</v>
       </c>
       <c r="L25">
-        <v>16.16</v>
+        <v>13.54333333333333</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2144,7 +2144,7 @@
         <v>257</v>
       </c>
       <c r="L27">
-        <v>13.97333333333333</v>
+        <v>11.62333333333333</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2182,7 +2182,7 @@
         <v>257</v>
       </c>
       <c r="L28">
-        <v>16.58275862068966</v>
+        <v>13.87241379310345</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2220,7 +2220,7 @@
         <v>257</v>
       </c>
       <c r="L29">
-        <v>16.28</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2258,7 +2258,7 @@
         <v>257</v>
       </c>
       <c r="L30">
-        <v>15.47857142857143</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2296,7 +2296,7 @@
         <v>258</v>
       </c>
       <c r="L31">
-        <v>16.23846153846154</v>
+        <v>13.89090909090909</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2334,7 +2334,7 @@
         <v>257</v>
       </c>
       <c r="L32">
-        <v>15.87</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2372,7 +2372,7 @@
         <v>257</v>
       </c>
       <c r="L33">
-        <v>15.46666666666667</v>
+        <v>13.38888888888889</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2410,7 +2410,7 @@
         <v>257</v>
       </c>
       <c r="L34">
-        <v>14.58333333333333</v>
+        <v>12.37333333333333</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2483,7 +2483,7 @@
         <v>257</v>
       </c>
       <c r="L36">
-        <v>16.28333333333333</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2521,7 +2521,7 @@
         <v>257</v>
       </c>
       <c r="L37">
-        <v>16.04</v>
+        <v>14.11666666666667</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2559,7 +2559,7 @@
         <v>257</v>
       </c>
       <c r="L38">
-        <v>15.74333333333333</v>
+        <v>13.74333333333333</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2597,7 +2597,7 @@
         <v>257</v>
       </c>
       <c r="L39">
-        <v>14.06666666666667</v>
+        <v>11.86333333333333</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2632,7 +2632,7 @@
         <v>257</v>
       </c>
       <c r="L40">
-        <v>16.276</v>
+        <v>14.232</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2670,7 +2670,7 @@
         <v>257</v>
       </c>
       <c r="L41">
-        <v>15.42307692307692</v>
+        <v>13.36538461538461</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2708,7 +2708,7 @@
         <v>257</v>
       </c>
       <c r="L42">
-        <v>14.92592592592593</v>
+        <v>12.41851851851852</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2746,7 +2746,7 @@
         <v>257</v>
       </c>
       <c r="L43">
-        <v>13.284</v>
+        <v>11.008</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2784,7 +2784,7 @@
         <v>257</v>
       </c>
       <c r="L44">
-        <v>12.54666666666667</v>
+        <v>8.836666666666668</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2822,7 +2822,7 @@
         <v>257</v>
       </c>
       <c r="L45">
-        <v>15.85172413793103</v>
+        <v>12.84827586206897</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2860,7 +2860,7 @@
         <v>257</v>
       </c>
       <c r="L46">
-        <v>11.5</v>
+        <v>8.403333333333332</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2898,7 +2898,7 @@
         <v>257</v>
       </c>
       <c r="L47">
-        <v>10.94666666666667</v>
+        <v>7.676666666666667</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2936,7 +2936,7 @@
         <v>257</v>
       </c>
       <c r="L48">
-        <v>12.35</v>
+        <v>8.623333333333333</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2974,7 +2974,7 @@
         <v>257</v>
       </c>
       <c r="L49">
-        <v>11.17142857142857</v>
+        <v>8.439285714285715</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -3012,7 +3012,7 @@
         <v>257</v>
       </c>
       <c r="L50">
-        <v>5.445833333333333</v>
+        <v>3.458333333333333</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3050,7 +3050,7 @@
         <v>257</v>
       </c>
       <c r="L51">
-        <v>11.79130434782609</v>
+        <v>8.847826086956522</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -3088,7 +3088,7 @@
         <v>257</v>
       </c>
       <c r="L52">
-        <v>11.75555555555555</v>
+        <v>8.233333333333334</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3126,7 +3126,7 @@
         <v>257</v>
       </c>
       <c r="L53">
-        <v>12.69666666666667</v>
+        <v>9.166666666666666</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3164,7 +3164,7 @@
         <v>257</v>
       </c>
       <c r="L54">
-        <v>12.79333333333333</v>
+        <v>9.363333333333333</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3202,7 +3202,7 @@
         <v>257</v>
       </c>
       <c r="L55">
-        <v>12.02</v>
+        <v>8.724137931034482</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3240,7 +3240,7 @@
         <v>257</v>
       </c>
       <c r="L56">
-        <v>14.77</v>
+        <v>10.94333333333333</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3278,7 +3278,7 @@
         <v>257</v>
       </c>
       <c r="L57">
-        <v>14.76</v>
+        <v>11.02333333333333</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3316,7 +3316,7 @@
         <v>257</v>
       </c>
       <c r="L58">
-        <v>11.72758620689655</v>
+        <v>8.73103448275862</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3354,7 +3354,7 @@
         <v>257</v>
       </c>
       <c r="L59">
-        <v>13.52333333333333</v>
+        <v>10.04333333333333</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3392,7 +3392,7 @@
         <v>257</v>
       </c>
       <c r="L60">
-        <v>14.26666666666667</v>
+        <v>10.69666666666667</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3430,7 +3430,7 @@
         <v>257</v>
       </c>
       <c r="L61">
-        <v>14.46666666666667</v>
+        <v>10.71333333333333</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3468,7 +3468,7 @@
         <v>257</v>
       </c>
       <c r="L62">
-        <v>15.60344827586207</v>
+        <v>11.63448275862069</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3506,7 +3506,7 @@
         <v>257</v>
       </c>
       <c r="L63">
-        <v>15.94642857142857</v>
+        <v>12.51034482758621</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3544,7 +3544,7 @@
         <v>257</v>
       </c>
       <c r="L64">
-        <v>15.25</v>
+        <v>10.975</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3582,7 +3582,7 @@
         <v>257</v>
       </c>
       <c r="L65">
-        <v>15.08</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3620,7 +3620,7 @@
         <v>257</v>
       </c>
       <c r="L66">
-        <v>18.10416666666667</v>
+        <v>14.40416666666667</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3658,7 +3658,7 @@
         <v>257</v>
       </c>
       <c r="L67">
-        <v>20.04444444444445</v>
+        <v>16.88888888888889</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3696,7 +3696,7 @@
         <v>257</v>
       </c>
       <c r="L68">
-        <v>19.1</v>
+        <v>16.36666666666667</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3734,7 +3734,7 @@
         <v>257</v>
       </c>
       <c r="L69">
-        <v>15.70416666666667</v>
+        <v>12.77083333333333</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3772,7 +3772,7 @@
         <v>257</v>
       </c>
       <c r="L70">
-        <v>16.50344827586207</v>
+        <v>13.08214285714286</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3810,7 +3810,7 @@
         <v>257</v>
       </c>
       <c r="L71">
-        <v>16.95333333333333</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3848,7 +3848,7 @@
         <v>257</v>
       </c>
       <c r="L72">
-        <v>20.17666666666667</v>
+        <v>16.57241379310345</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3886,7 +3886,7 @@
         <v>257</v>
       </c>
       <c r="L73">
-        <v>19.73333333333333</v>
+        <v>16.39666666666666</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3924,7 +3924,7 @@
         <v>257</v>
       </c>
       <c r="L74">
-        <v>19.72608695652174</v>
+        <v>16.73913043478261</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3962,7 +3962,7 @@
         <v>257</v>
       </c>
       <c r="L75">
-        <v>20.24</v>
+        <v>16.92333333333333</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4000,7 +4000,7 @@
         <v>257</v>
       </c>
       <c r="L76">
-        <v>19.57857142857143</v>
+        <v>16.87142857142857</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4038,7 +4038,7 @@
         <v>257</v>
       </c>
       <c r="L77">
-        <v>20.28666666666667</v>
+        <v>17.84333333333333</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4076,7 +4076,7 @@
         <v>257</v>
       </c>
       <c r="L78">
-        <v>20.12666666666667</v>
+        <v>17.50666666666667</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4114,7 +4114,7 @@
         <v>257</v>
       </c>
       <c r="L79">
-        <v>20.45333333333333</v>
+        <v>17.94333333333333</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4152,7 +4152,7 @@
         <v>257</v>
       </c>
       <c r="L80">
-        <v>20.34444444444444</v>
+        <v>17.15925925925926</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -4190,7 +4190,7 @@
         <v>257</v>
       </c>
       <c r="L81">
-        <v>20.17666666666667</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4228,7 +4228,7 @@
         <v>257</v>
       </c>
       <c r="L82">
-        <v>20.26666666666667</v>
+        <v>17.34137931034483</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4266,7 +4266,7 @@
         <v>257</v>
       </c>
       <c r="L83">
-        <v>20.47333333333334</v>
+        <v>17.69666666666667</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4304,7 +4304,7 @@
         <v>257</v>
       </c>
       <c r="L84">
-        <v>13.33333333333333</v>
+        <v>10.07333333333333</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4342,7 +4342,7 @@
         <v>257</v>
       </c>
       <c r="L85">
-        <v>14.46</v>
+        <v>10.86666666666667</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4380,7 +4380,7 @@
         <v>257</v>
       </c>
       <c r="L86">
-        <v>15.175</v>
+        <v>11.55357142857143</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4418,7 +4418,7 @@
         <v>257</v>
       </c>
       <c r="L87">
-        <v>13.424</v>
+        <v>9.872</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4456,7 +4456,7 @@
         <v>257</v>
       </c>
       <c r="L88">
-        <v>19.27333333333333</v>
+        <v>16.22666666666667</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4494,7 +4494,7 @@
         <v>257</v>
       </c>
       <c r="L89">
-        <v>18.8</v>
+        <v>15.84333333333333</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4532,7 +4532,7 @@
         <v>257</v>
       </c>
       <c r="L90">
-        <v>12.40666666666667</v>
+        <v>9.106666666666666</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4605,7 +4605,7 @@
         <v>257</v>
       </c>
       <c r="L92">
-        <v>13.81666666666667</v>
+        <v>10.17666666666667</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4643,7 +4643,7 @@
         <v>257</v>
       </c>
       <c r="L93">
-        <v>13.05333333333333</v>
+        <v>9.696551724137931</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4681,7 +4681,7 @@
         <v>257</v>
       </c>
       <c r="L94">
-        <v>12.54285714285714</v>
+        <v>9.360000000000001</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4719,7 +4719,7 @@
         <v>257</v>
       </c>
       <c r="L95">
-        <v>13.54333333333333</v>
+        <v>10.00333333333333</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4757,7 +4757,7 @@
         <v>257</v>
       </c>
       <c r="L96">
-        <v>14.84</v>
+        <v>10.77333333333333</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4795,7 +4795,7 @@
         <v>257</v>
       </c>
       <c r="L97">
-        <v>14.93571428571429</v>
+        <v>9.796428571428573</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4833,7 +4833,7 @@
         <v>257</v>
       </c>
       <c r="L98">
-        <v>13.36206896551724</v>
+        <v>9.179310344827586</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4871,7 +4871,7 @@
         <v>257</v>
       </c>
       <c r="L99">
-        <v>18.38333333333333</v>
+        <v>14.88333333333333</v>
       </c>
     </row>
   </sheetData>
